--- a/data/trans_dic/IP11C$medico-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$medico-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria y consultaron a un médico/a o enfermero/a</t>
+          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria y consultaron a un médico/a o enfermero/a (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,72</t>
+          <t>0,0; 69,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 81,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,51</t>
+          <t>0,0; 53,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,91</t>
+          <t>0,0; 57,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,39; 48,26</t>
+          <t>6,54; 49,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,86</t>
+          <t>0,0; 44,1</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,83</t>
+          <t>0,0; 64,24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,17</t>
+          <t>0,0; 46,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,82</t>
+          <t>0,0; 31,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,96</t>
+          <t>0,0; 38,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,13; 30,83</t>
+          <t>2,97; 28,52</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,37</t>
+          <t>0,0; 26,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,17 +997,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1016,42 +1017,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,22</t>
+          <t>0,0; 37,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,67; 39,08</t>
+          <t>4,69; 39,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,56</t>
+          <t>0,0; 19,09</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 18,88</t>
+          <t>2,56; 21,63</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,23</t>
+          <t>0,0; 59,34</t>
         </is>
       </c>
     </row>
@@ -1136,37 +1137,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,01</t>
+          <t>0,0; 46,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,45</t>
+          <t>0,0; 49,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,23</t>
+          <t>0,0; 36,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1176,17 +1177,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 35,65</t>
+          <t>4,49; 36,93</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,54</t>
+          <t>0,0; 26,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1281,12 +1282,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1306,12 +1307,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,24 +1322,24 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,09</t>
+          <t>0,0; 65,46</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,99</t>
+          <t>0,0; 81,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,0; 49,06</t>
+          <t>6,98; 48,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,92</t>
+          <t>0,0; 55,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 72,56</t>
+          <t>0,0; 71,25</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,77; 31,73</t>
+          <t>3,86; 30,72</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,51</t>
+          <t>0,0; 38,86</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,05</t>
+          <t>0,0; 35,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,98</t>
+          <t>0,0; 20,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,08</t>
+          <t>0,0; 54,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,63</t>
+          <t>0,0; 22,65</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,39</t>
+          <t>0,0; 14,19</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,69</t>
+          <t>0,0; 38,31</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,64</t>
+          <t>0,0; 44,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,07</t>
+          <t>0,0; 35,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,02</t>
+          <t>0,0; 26,76</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,33</t>
+          <t>0,0; 32,1</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,73; 21,0</t>
+          <t>3,65; 20,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,18; 11,3</t>
+          <t>1,18; 13,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,83</t>
+          <t>0,0; 30,62</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,39; 24,22</t>
+          <t>7,41; 24,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,76; 17,17</t>
+          <t>5,37; 16,43</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,81; 17,83</t>
+          <t>1,75; 16,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,69</t>
+          <t>0,0; 31,1</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,69; 19,83</t>
+          <t>7,75; 19,44</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4,57; 12,31</t>
+          <t>4,35; 12,46</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,15; 10,88</t>
+          <t>1,51; 11,85</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,22; 24,39</t>
+          <t>3,24; 23,58</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria y consultaron a un médico/a o enfermero/a (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1178</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>994</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1631</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2809</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>994</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3209</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2569</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4018</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3572</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>794; 5945</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3768</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4464</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1628</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2234</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4515</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3178</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2606</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>590; 5664</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3245</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>529</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>529</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 1875</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2305</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>644; 5379</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2254</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>642; 5419</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2279</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>806</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1344</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1516</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2150</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1517</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3187</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3948</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2850</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2046</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>666; 5476</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3354</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2992</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1438</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1438</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2790</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 1975</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2790</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2660</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1314</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2784</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1314</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2784</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2633</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>918; 6349</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3290</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3258</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>811; 6462</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3699</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1377</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1377</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4124</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4124</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3737</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4196</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4602</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4152</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2510</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3058</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3588</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3108</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>2236</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>6890</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>7359</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>3040</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>2439</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>10312</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>9595</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3040</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>3841</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>1290; 7111</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>610; 6728</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>0; 5252</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>3448; 11613</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>3937; 12053</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>715; 6852</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>0; 7475</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>6338; 15907</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>5443; 15581</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>967; 7594</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>1334; 9712</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP11C$medico-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$medico-Provincia-trans_dic.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,33</t>
+          <t>0,0; 53,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,94</t>
+          <t>0,0; 57,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,54; 49,0</t>
+          <t>6,58; 48,77</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,1</t>
+          <t>0,0; 50,29</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,24</t>
+          <t>0,0; 58,86</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,75</t>
+          <t>0,0; 48,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -882,12 +882,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,15</t>
+          <t>0,0; 25,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,31</t>
+          <t>0,0; 47,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -902,12 +902,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 28,52</t>
+          <t>3,03; 28,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,7</t>
+          <t>0,0; 23,56</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,04</t>
+          <t>0,0; 36,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,69; 39,18</t>
+          <t>4,63; 34,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1037,12 +1037,12 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,09</t>
+          <t>0,0; 20,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,56; 21,63</t>
+          <t>2,57; 20,4</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,34</t>
+          <t>0,0; 53,81</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,65</t>
+          <t>0,0; 45,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,37</t>
+          <t>0,0; 44,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,38</t>
+          <t>0,0; 36,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,49; 36,93</t>
+          <t>0,0; 34,24</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,24</t>
+          <t>0,0; 22,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,46</t>
+          <t>0,0; 65,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1442,12 +1442,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,98; 48,27</t>
+          <t>3,57; 47,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,07</t>
+          <t>0,0; 62,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1457,17 +1457,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,25</t>
+          <t>0,0; 71,4</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,86; 30,72</t>
+          <t>3,68; 31,27</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,86</t>
+          <t>0,0; 38,45</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,31</t>
+          <t>0,0; 34,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,14</t>
+          <t>0,0; 19,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1592,17 +1592,17 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,66</t>
+          <t>0,0; 52,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,65</t>
+          <t>0,0; 24,13</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,19</t>
+          <t>0,0; 12,46</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,31</t>
+          <t>0,0; 44,29</t>
         </is>
       </c>
     </row>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,77</t>
+          <t>0,0; 44,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,82</t>
+          <t>0,0; 37,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1737,12 +1737,12 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,76</t>
+          <t>0,0; 24,25</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,1</t>
+          <t>0,0; 32,28</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,65; 20,14</t>
+          <t>3,64; 21,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,18; 13,01</t>
+          <t>1,17; 11,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1852,47 +1852,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,62</t>
+          <t>0,0; 30,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,41; 24,96</t>
+          <t>7,67; 25,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,37; 16,43</t>
+          <t>5,31; 16,95</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,75; 16,83</t>
+          <t>1,82; 17,13</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,1</t>
+          <t>0,0; 29,46</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,75; 19,44</t>
+          <t>7,71; 20,07</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4,35; 12,46</t>
+          <t>4,53; 12,98</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,51; 11,85</t>
+          <t>1,53; 10,81</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,24; 23,58</t>
+          <t>2,53; 24,69</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4018</t>
+          <t>0; 4017</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3572</t>
+          <t>0; 3575</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>794; 5945</t>
+          <t>799; 5918</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 3768</t>
+          <t>0; 4297</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 4464</t>
+          <t>0; 4090</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4515</t>
+          <t>0; 4717</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3178</t>
+          <t>0; 2607</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2606</t>
+          <t>0; 3260</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>590; 5664</t>
+          <t>602; 5707</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 3245</t>
+          <t>0; 2863</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2305</t>
+          <t>0; 2242</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>644; 5379</t>
+          <t>636; 4744</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2665,12 +2665,12 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 2254</t>
+          <t>0; 2444</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>642; 5419</t>
+          <t>643; 5109</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 2279</t>
+          <t>0; 2067</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3187</t>
+          <t>0; 3091</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3948</t>
+          <t>0; 3518</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2850</t>
+          <t>0; 2871</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>666; 5476</t>
+          <t>0; 5078</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 3354</t>
+          <t>0; 2914</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 2660</t>
+          <t>0; 2662</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>918; 6349</t>
+          <t>470; 6218</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3290</t>
+          <t>0; 3714</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -3289,17 +3289,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 3258</t>
+          <t>0; 3265</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>811; 6462</t>
+          <t>773; 6577</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 3699</t>
+          <t>0; 3660</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 4124</t>
+          <t>0; 4084</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 4124</t>
+          <t>0; 3961</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3492,17 +3492,17 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3737</t>
+          <t>0; 3579</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 4196</t>
+          <t>0; 4471</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 4602</t>
+          <t>0; 4042</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0; 4152</t>
+          <t>0; 4801</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2510</t>
+          <t>0; 2503</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 3058</t>
+          <t>0; 3206</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 3588</t>
+          <t>0; 3251</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0; 3108</t>
+          <t>0; 3124</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1290; 7111</t>
+          <t>1284; 7505</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>610; 6728</t>
+          <t>607; 6107</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3888,47 +3888,47 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>0; 5252</t>
+          <t>0; 5219</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3448; 11613</t>
+          <t>3566; 11877</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3937; 12053</t>
+          <t>3899; 12435</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>715; 6852</t>
+          <t>741; 6975</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>0; 7475</t>
+          <t>0; 7081</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>6338; 15907</t>
+          <t>6305; 16421</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5443; 15581</t>
+          <t>5667; 16233</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>967; 7594</t>
+          <t>980; 6928</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1334; 9712</t>
+          <t>1042; 10170</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP11C$medico-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$medico-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,29 +649,29 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>21,64%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>15,85%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>25,61%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>31,6%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>21,64%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -679,12 +679,12 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,79</t>
+          <t>0,0; 61,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -727,17 +727,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 65,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,31</t>
+          <t>0,0; 69,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,17 +747,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,58; 48,77</t>
+          <t>6,39; 48,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,29</t>
+          <t>0,0; 44,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,86</t>
+          <t>0,0; 66,05</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>5,95%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9,31%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>16,85%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,95%</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -862,12 +862,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,84</t>
+          <t>0,0; 28,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 38,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -882,12 +882,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,55</t>
+          <t>0,0; 47,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -902,12 +902,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,03; 28,74</t>
+          <t>3,13; 30,83</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,56</t>
+          <t>0,0; 26,37</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -944,17 +944,17 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 39,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,67; 39,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,37 +1012,37 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 36,04</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>4,63; 34,56</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,7</t>
+          <t>0,0; 22,56</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 20,4</t>
+          <t>2,57; 18,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,81</t>
+          <t>0,0; 52,1</t>
         </is>
       </c>
     </row>
@@ -1069,29 +1069,29 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16,81%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8,81%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>77,11%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>11,8%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>16,81%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,35%</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,24</t>
+          <t>0,0; 50,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1147,17 +1147,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 37,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,0</t>
+          <t>0,0; 45,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1167,17 +1167,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,65</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,24</t>
+          <t>4,57; 35,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,8</t>
+          <t>0,0; 27,54</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>32,76%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>51,54%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>32,76%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1277,14 +1277,14 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1297,32 +1297,32 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 100,0</t>
-        </is>
-      </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,52</t>
+          <t>0,0; 66,09</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1349,17 +1349,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1369,17 +1369,17 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1417,17 +1417,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 81,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,0; 49,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 49,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1437,17 +1437,17 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,57; 47,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1457,17 +1457,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,4</t>
+          <t>0,0; 72,56</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,68; 31,27</t>
+          <t>3,77; 31,73</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,45</t>
+          <t>0,0; 31,51</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1504,17 +1504,17 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 36,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 22,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1572,17 +1572,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 55,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1592,17 +1592,17 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,13</t>
+          <t>0,0; 21,63</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,46</t>
+          <t>0,0; 12,39</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,29</t>
+          <t>0,0; 38,1</t>
         </is>
       </c>
     </row>
@@ -1629,32 +1629,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
           <t>10,86%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>8,14%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1697,12 +1697,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 36,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,65</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 55,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1737,12 +1737,12 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,25</t>
+          <t>0,0; 22,02</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,28</t>
+          <t>0,0; 26,33</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>14,81%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>10,03%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>7,46%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>11,16%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>9,69%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>4,32%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>14,81%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>10,03%</t>
-        </is>
-      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,64; 21,26</t>
+          <t>7,39; 24,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,17; 11,81</t>
+          <t>4,76; 17,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,81; 17,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,43</t>
+          <t>0,0; 33,93</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,67; 25,53</t>
+          <t>3,73; 21,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,31; 16,95</t>
+          <t>1,18; 11,3</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,82; 17,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,46</t>
+          <t>0,0; 27,68</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,71; 20,07</t>
+          <t>7,69; 19,83</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4,53; 12,98</t>
+          <t>4,57; 12,31</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,53; 10,81</t>
+          <t>1,15; 10,88</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,53; 24,69</t>
+          <t>3,1; 25,23</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2083,32 +2083,32 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,29 +2141,29 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1631</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1178</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>994</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1631</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2171,32 +2171,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>983</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2809</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
           <t>977</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2809</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>983</t>
         </is>
       </c>
     </row>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3209</t>
+          <t>0; 4635</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2219,17 +2219,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4064</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2569</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4017</t>
+          <t>0; 3206</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -2239,17 +2239,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3575</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2973</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>799; 5918</t>
+          <t>776; 5855</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 4297</t>
+          <t>0; 3833</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 4090</t>
+          <t>0; 3950</t>
         </is>
       </c>
     </row>
@@ -2286,32 +2286,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>1628</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2422,12 +2422,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4717</t>
+          <t>0; 2940</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2650</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2607</t>
+          <t>0; 4555</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3260</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>602; 5707</t>
+          <t>621; 6123</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 2863</t>
+          <t>0; 3205</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -2504,27 +2504,27 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,12 +2557,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>529</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -2572,39 +2572,39 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>529</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>529</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>308</t>
         </is>
       </c>
     </row>
@@ -2625,12 +2625,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2440</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>642; 5365</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2640,17 +2640,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 1875</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2242</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>636; 4744</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2660,17 +2660,17 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 1760</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 2444</t>
+          <t>0; 2664</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>643; 5109</t>
+          <t>643; 4729</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 2067</t>
+          <t>0; 1785</t>
         </is>
       </c>
     </row>
@@ -2697,27 +2697,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -2727,12 +2727,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,29 +2765,29 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1344</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1526</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>806</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1344</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2795,32 +2795,32 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2150</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
           <t>690</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1516</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2150</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>690</t>
-        </is>
-      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1526</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3091</t>
+          <t>0; 4034</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2843,17 +2843,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2916</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 1979</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3518</t>
+          <t>0; 3075</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2863,17 +2863,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2871</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2046</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5078</t>
+          <t>677; 5287</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2883,12 +2883,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 2914</t>
+          <t>0; 3520</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 2992</t>
+          <t>0; 3030</t>
         </is>
       </c>
     </row>
@@ -2905,32 +2905,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>1438</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3041,32 +3041,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 1975</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>0; 2790</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 1975</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 2662</t>
+          <t>0; 2685</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -3113,17 +3113,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -3133,17 +3133,17 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>739</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -3201,17 +3201,17 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -3249,17 +3249,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2634</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>920; 6452</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2982</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -3269,17 +3269,17 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 2633</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>470; 6218</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3714</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -3289,17 +3289,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 3265</t>
+          <t>0; 3318</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>773; 6577</t>
+          <t>792; 6674</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 3660</t>
+          <t>0; 2999</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -3336,17 +3336,17 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,12 +3389,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -3404,39 +3404,39 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>957</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
           <t>1377</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>1320</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>1377</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>1320</t>
-        </is>
-      </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>957</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4211</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4705</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3472,17 +3472,17 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3811</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 4084</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 3961</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3492,17 +3492,17 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3579</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 4471</t>
+          <t>0; 4007</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 4042</t>
+          <t>0; 4018</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0; 4801</t>
+          <t>0; 4105</t>
         </is>
       </c>
     </row>
@@ -3529,32 +3529,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>695</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
           <t>609</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3079</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2503</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 3206</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3118</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 3251</t>
+          <t>0; 2953</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0; 3124</t>
+          <t>0; 2549</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -3737,37 +3737,37 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3805,62 +3805,62 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>6890</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>7359</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>3040</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2483</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>3422</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>2236</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1402</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>6890</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>7359</t>
-        </is>
-      </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>1291</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>10312</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>9595</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
           <t>3040</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>2439</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>10312</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>9595</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>3040</t>
-        </is>
-      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>3774</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1284; 7505</t>
+          <t>3440; 11266</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>607; 6107</t>
+          <t>3493; 12598</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>739; 7259</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>0; 5219</t>
+          <t>0; 7549</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3566; 11877</t>
+          <t>1317; 7413</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3899; 12435</t>
+          <t>611; 5845</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>741; 6975</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>0; 7081</t>
+          <t>0; 4756</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>6305; 16421</t>
+          <t>6291; 16223</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5667; 16233</t>
+          <t>5717; 15402</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>980; 6928</t>
+          <t>737; 6970</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1042; 10170</t>
+          <t>1223; 9950</t>
         </is>
       </c>
     </row>
